--- a/요구사항명세서(3조).xlsx
+++ b/요구사항명세서(3조).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항 명세" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="146">
   <si>
     <t>ID</t>
   </si>
@@ -42,9 +42,6 @@
     <t>계정</t>
   </si>
   <si>
-    <t>마스터/관리자 계정</t>
-  </si>
-  <si>
     <t>초기 계정 생성</t>
   </si>
   <si>
@@ -249,72 +246,24 @@
     <t>권한을 부여받은 경우 해당 권한에 대한 메뉴만 나타나며 여기에만 접근할 수 있어야 한다.</t>
   </si>
   <si>
-    <t>CTRL-001</t>
-  </si>
-  <si>
-    <t>관제</t>
-  </si>
-  <si>
-    <t>순찰 구역 설정</t>
-  </si>
-  <si>
-    <t>순찰 구역 수정/삭제</t>
-  </si>
-  <si>
-    <t>지도 위에 체크포인트를 찍어 순찰 구역을 등록할 수 있어야 한다.</t>
-  </si>
-  <si>
-    <t>CTRL-002</t>
-  </si>
-  <si>
-    <t>순찰 구역 지정</t>
-  </si>
-  <si>
-    <t>CTRL-003</t>
-  </si>
-  <si>
-    <t>CTRL-004</t>
-  </si>
-  <si>
-    <t>CTRL-005</t>
-  </si>
-  <si>
-    <t>CTRL-006</t>
-  </si>
-  <si>
     <t>메인 페이지</t>
   </si>
   <si>
     <t>실시간 영상 관제</t>
   </si>
   <si>
-    <t>CTRL-007</t>
-  </si>
-  <si>
     <t>관제 메뉴 관리</t>
   </si>
   <si>
-    <t>CTRL-008</t>
-  </si>
-  <si>
     <t>이벤트 알림 관리</t>
   </si>
   <si>
-    <t>CTRL-009</t>
-  </si>
-  <si>
     <t>지도 기반 위치 관제</t>
   </si>
   <si>
-    <t>CTRL-010</t>
-  </si>
-  <si>
     <t>사용자 인증 관리</t>
   </si>
   <si>
-    <t>CTRL-011</t>
-  </si>
-  <si>
     <t>AI 분석된 영상 화면</t>
   </si>
   <si>
@@ -324,66 +273,42 @@
     <t>실시간으로 스트리밍되는 영상 내에서 DB에 등록된 인물을 탐지해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-012</t>
-  </si>
-  <si>
     <t>탐지 대상 강조 표시</t>
   </si>
   <si>
     <t>영상에서 탐지된 인물 주변에 빨간색 바운딩 박스를 표시하여 강조해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-013</t>
-  </si>
-  <si>
     <t>신원 정보 표시</t>
   </si>
   <si>
     <t>탐지된 인물의 이름 및 프로필 정보를 화면에 표시해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-014</t>
-  </si>
-  <si>
     <t>등록 사유 표시</t>
   </si>
   <si>
     <t>탐지된 인물이 DB에 등록된 사유를 화면에 함께 표시해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-015</t>
-  </si>
-  <si>
     <t>탐지 결과 검토</t>
   </si>
   <si>
     <t>관제 인원은 시스템 화면을 통해 AI가 실시간으로 탐지한 대상자의 정보를 확인할 수 있어야 한다.</t>
   </si>
   <si>
-    <t>CTRL-016</t>
-  </si>
-  <si>
     <t>오인식 여부 판단</t>
   </si>
   <si>
     <t>관제 인원이 탐지 대상자와 실제 등록된 인물이 일치하는지 오인식 여부를 직접 판단할 수 있어야 한다.</t>
   </si>
   <si>
-    <t>CTRL-017</t>
-  </si>
-  <si>
     <t>제외 요청 등록</t>
   </si>
   <si>
-    <t>CTRL-018</t>
-  </si>
-  <si>
     <t>제외 사유 제출</t>
   </si>
   <si>
-    <t>CTRL-019</t>
-  </si>
-  <si>
     <t>로그</t>
   </si>
   <si>
@@ -393,18 +318,9 @@
     <t>탐지 발생 장소 발생 시간 신원 정보 등록 사유가 포함된 통합 로그를 기록해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-020</t>
-  </si>
-  <si>
     <t>수집된 관제 로그를 엑셀(.xlsx) 또는 JSON 파일 형태로 내보내기(다운로드)할 수 있어야 한다.</t>
   </si>
   <si>
-    <t>CTRL-021</t>
-  </si>
-  <si>
-    <t>CTRL-022</t>
-  </si>
-  <si>
     <t>경고 이벤트 현황판</t>
   </si>
   <si>
@@ -414,54 +330,24 @@
     <t>검사 대상이 영상에서 탐지된 경우 알림 패널에 간략한 요약 정보를 즉각 표시해야 한다.</t>
   </si>
   <si>
-    <t>CTRL-023</t>
-  </si>
-  <si>
     <t>탐지 이력 요약 조회</t>
   </si>
   <si>
-    <t>CTRL-024</t>
-  </si>
-  <si>
     <t>SNS 알림 전송</t>
   </si>
   <si>
-    <t>CTRL-025</t>
-  </si>
-  <si>
     <t>상세 로그 조회</t>
   </si>
   <si>
     <t>현황판의 특정 로그 항목을 클릭하면 해당 이벤트의 상세 탐지 로그를 조회할 수 있어야 한다.</t>
   </si>
   <si>
-    <t>CTRL-026</t>
-  </si>
-  <si>
     <t>지도</t>
   </si>
   <si>
     <t>미니맵 제공</t>
   </si>
   <si>
-    <t>CTRL-027</t>
-  </si>
-  <si>
-    <t>마킹 도형</t>
-  </si>
-  <si>
-    <t>관제 인원이 현장 파악을 쉽게 하도록 지도 위에 핀 또는 마킹 도형을 수정/편집할 수 있어야 한다.</t>
-  </si>
-  <si>
-    <t>CTRL-028</t>
-  </si>
-  <si>
-    <t>경로</t>
-  </si>
-  <si>
-    <t>순찰 대상이 설정된 체크포인트 순서대로 이동 중인 경로를 지도 위에 선(Line)으로 시각화해야 한다.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2489,112 +2375,377 @@
   <si>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등록한</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순찰</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경로의</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름을</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정할</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우측</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상단</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비로그인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상태에서는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로그인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회원가입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메뉴가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표시되어야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오른쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미니맵</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어디인지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2605,17 +2756,53 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미니맵이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2626,17 +2813,15 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2647,7 +2832,6 @@
     </r>
     <r>
       <rPr>
-        <strike/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -2660,112 +2844,190 @@
   <si>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이미</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등록된</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순찰</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경로를</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정할</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오른쪽에</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이벤트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현황을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2776,17 +3038,53 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>패널이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2797,17 +3095,15 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="돋움"/>
@@ -2818,7 +3114,6 @@
     </r>
     <r>
       <rPr>
-        <strike/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -2830,61 +3125,265 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순찰</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능을</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>활성화</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나와야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왼쪽에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레이아웃으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잡아야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마스터</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
@@ -2894,1279 +3393,329 @@
     </r>
     <r>
       <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비활성화</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>할</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계정</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>등록</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>된</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순찰</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경로를</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>삭제할</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
+      <t>CTRL-00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우측</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상단</t>
+      <t>CTRL-00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비로그인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상태에서는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로그인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회원가입</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>메뉴가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>표시되어야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오른쪽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하단</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미니맵</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장소가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어디인지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확인할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미니맵이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오른쪽에</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>영상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이벤트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>발생</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>현황을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실시간으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확인할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>패널이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있어야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분석된</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실시간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>영상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>화면이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나와야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>화면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>왼쪽에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>레이아웃으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잡아야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
+      <t>CTRL-003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-004</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-008</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-009</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-010</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-011</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-012</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-013</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-014</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-016</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-018</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CTRL-021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
     </r>
   </si>
 </sst>
@@ -4174,7 +3723,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4215,28 +3764,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
@@ -4288,9 +3815,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4328,22 +3855,31 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4626,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="8" customWidth="1"/>
@@ -4670,425 +4206,408 @@
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" ht="13.5" customHeight="1">
       <c r="A4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1">
       <c r="A5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="13.5" customHeight="1">
       <c r="A6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="13.5" customHeight="1">
       <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="13.5" customHeight="1">
       <c r="A8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="13.5" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="13.5" customHeight="1">
       <c r="A10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="13.5" customHeight="1">
       <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="13.5" customHeight="1">
       <c r="A12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" ht="13.5" customHeight="1">
       <c r="A13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1">
       <c r="A14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:6" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="1:6" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="15"/>
     </row>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A16" s="10" t="s">
+    <row r="17" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="7"/>
+      <c r="E17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="15"/>
     </row>
-    <row r="17" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="11" t="s">
+    <row r="18" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A18" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="15"/>
     </row>
-    <row r="18" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A18" s="10" t="s">
+    <row r="19" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="7"/>
+      <c r="D19" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="15"/>
     </row>
-    <row r="19" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A19" s="10" t="s">
+    <row r="20" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A20" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="7"/>
+      <c r="E20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="15"/>
     </row>
-    <row r="20" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A20" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="11" t="s">
+    <row r="21" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A21" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="7"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="15"/>
     </row>
-    <row r="21" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A21" s="10" t="s">
+    <row r="22" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A22" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="7"/>
+      <c r="D22" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="15"/>
     </row>
-    <row r="22" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="11" t="s">
+    <row r="23" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A23" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="15"/>
     </row>
-    <row r="23" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A23" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="11" t="s">
+    <row r="24" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="15"/>
     </row>
-    <row r="24" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A24" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="11" t="s">
+    <row r="25" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="15"/>
     </row>
-    <row r="25" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A25" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="11" t="s">
+    <row r="26" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A26" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="15"/>
     </row>
-    <row r="26" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A26" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A27" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+    <row r="27" spans="1:11" s="16" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A28" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" s="7"/>
+      <c r="A28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>123</v>
+      </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5096,20 +4615,20 @@
       <c r="K28" s="7"/>
     </row>
     <row r="29" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F29" s="7"/>
+      <c r="A29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -5117,20 +4636,22 @@
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A30" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F30" s="7"/>
+      <c r="A30" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -5138,20 +4659,22 @@
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A31" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="A31" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F31" s="7"/>
+      <c r="E31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -5159,21 +4682,21 @@
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A32" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="17"/>
+      <c r="A32" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="18"/>
       <c r="C32" s="10" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>165</v>
+        <v>117</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
@@ -5182,20 +4705,20 @@
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A33" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="17"/>
+      <c r="A33" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="18"/>
       <c r="C33" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -5203,22 +4726,20 @@
       <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A34" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="17"/>
+      <c r="A34" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="18"/>
       <c r="C34" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>162</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -5226,22 +4747,20 @@
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A35" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="17"/>
+      <c r="A35" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="18"/>
       <c r="C35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>160</v>
-      </c>
+      <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5249,22 +4768,20 @@
       <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A36" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="17"/>
+      <c r="A36" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="18"/>
       <c r="C36" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>158</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
@@ -5272,18 +4789,18 @@
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A37" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="17"/>
+      <c r="A37" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="18"/>
       <c r="C37" s="10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -5293,18 +4810,18 @@
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A38" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" s="17"/>
+      <c r="A38" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="18"/>
       <c r="C38" s="10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -5314,18 +4831,18 @@
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A39" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="17"/>
+      <c r="A39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="18"/>
       <c r="C39" s="10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -5335,20 +4852,20 @@
       <c r="K39" s="7"/>
     </row>
     <row r="40" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A40" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B40" s="17"/>
+      <c r="A40" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B40" s="18"/>
       <c r="C40" s="10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F40" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
@@ -5356,39 +4873,39 @@
       <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A41" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="17"/>
+      <c r="A41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="18"/>
       <c r="C41" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
     </row>
     <row r="42" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A42" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" s="17"/>
+      <c r="A42" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="18"/>
       <c r="C42" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -5398,41 +4915,41 @@
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A43" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" s="17"/>
+      <c r="A43" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" s="18"/>
       <c r="C43" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
     </row>
     <row r="44" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A44" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="17"/>
+      <c r="A44" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" s="18"/>
       <c r="C44" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -5440,39 +4957,39 @@
       <c r="K44" s="7"/>
     </row>
     <row r="45" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A45" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" s="17"/>
+      <c r="A45" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="18"/>
       <c r="C45" s="10" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>123</v>
+        <v>103</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="7"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
     </row>
     <row r="46" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A46" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" s="17"/>
+      <c r="A46" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="18"/>
       <c r="C46" s="10" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -5482,39 +4999,39 @@
       <c r="K46" s="7"/>
     </row>
     <row r="47" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A47" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="17"/>
+      <c r="A47" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" s="18"/>
       <c r="C47" s="10" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
     </row>
     <row r="48" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A48" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" s="17"/>
+      <c r="A48" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48" s="18"/>
       <c r="C48" s="10" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>130</v>
+        <v>108</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -5523,136 +5040,11 @@
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A49" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A50" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A51" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A52" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-    </row>
-    <row r="53" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A53" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-    </row>
-    <row r="54" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A54" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B3:B26"/>
-    <mergeCell ref="B27:B54"/>
+    <mergeCell ref="B28:B48"/>
+    <mergeCell ref="C3:C5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
